--- a/artfynd/A 25118-2026 artfynd.xlsx
+++ b/artfynd/A 25118-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134139583</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>134149451</v>
       </c>
       <c r="B3" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134149427</v>
       </c>
       <c r="B4" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>134139582</v>
       </c>
       <c r="B5" t="n">
-        <v>98046</v>
+        <v>98053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>134149270</v>
       </c>
       <c r="B6" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134297169</v>
       </c>
       <c r="B8" t="n">
-        <v>99101</v>
+        <v>99108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>134139575</v>
       </c>
       <c r="B10" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 25118-2026 artfynd.xlsx
+++ b/artfynd/A 25118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134139583</v>
+        <v>134139578</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591262</v>
+        <v>591187</v>
       </c>
       <c r="R2" t="n">
-        <v>6559078</v>
+        <v>6559160</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Börjar blomma</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,52 +785,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134149451</v>
+        <v>134139575</v>
       </c>
       <c r="B3" t="n">
-        <v>98053</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långstjärten O om , Srm</t>
+          <t>Långstjärten, Långstjärten, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591213</v>
+        <v>591318</v>
       </c>
       <c r="R3" t="n">
-        <v>6559053</v>
+        <v>6559094</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,99 +860,99 @@
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134149427</v>
+        <v>134139573</v>
       </c>
       <c r="B4" t="n">
-        <v>106317</v>
+        <v>58136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långstjärten O om , Srm</t>
+          <t>Långstjärten, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591213</v>
+        <v>591110</v>
       </c>
       <c r="R4" t="n">
-        <v>6559053</v>
+        <v>6559308</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,73 +979,85 @@
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134139582</v>
+        <v>134139574</v>
       </c>
       <c r="B5" t="n">
-        <v>98053</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591216</v>
+        <v>591317</v>
       </c>
       <c r="R5" t="n">
-        <v>6559236</v>
+        <v>6559253</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134149270</v>
+        <v>134318320</v>
       </c>
       <c r="B6" t="n">
-        <v>106317</v>
+        <v>98219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591053</v>
+        <v>591072</v>
       </c>
       <c r="R6" t="n">
-        <v>6559182</v>
+        <v>6559189</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,9 +1224,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1236,67 +1237,59 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134139573</v>
+        <v>134297109</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>98623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220007</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Missne</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calla palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långstjärten, Srm</t>
+          <t>Långstjärten ONO om , Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591110</v>
+        <v>591239</v>
       </c>
       <c r="R7" t="n">
-        <v>6559308</v>
+        <v>6559260</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,87 +1316,95 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kärr</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134297169</v>
+        <v>134139583</v>
       </c>
       <c r="B8" t="n">
-        <v>99108</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långstjärten ONO om , Srm</t>
+          <t>Långstjärten, Långstjärten, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591239</v>
+        <v>591262</v>
       </c>
       <c r="R8" t="n">
-        <v>6559260</v>
+        <v>6559078</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,95 +1431,96 @@
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Börjar blomma</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134139574</v>
+        <v>134149270</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>106324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långstjärten, Långstjärten, Srm</t>
+          <t>Långstjärten O om , Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591317</v>
+        <v>591053</v>
       </c>
       <c r="R9" t="n">
-        <v>6559253</v>
+        <v>6559182</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1545,94 +1547,99 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134139575</v>
+        <v>134149427</v>
       </c>
       <c r="B10" t="n">
-        <v>79985</v>
+        <v>106324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långstjärten, Långstjärten, Srm</t>
+          <t>Långstjärten O om , Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591318</v>
+        <v>591213</v>
       </c>
       <c r="R10" t="n">
-        <v>6559094</v>
+        <v>6559053</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,42 +1666,1108 @@
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134314782</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>591156</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6559159</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134318567</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>591080</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6559138</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134318573</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107695</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221705</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ängskovall</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591080</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6559138</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134139582</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långstjärten, Långstjärten, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>591216</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6559236</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Göran Ekström</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Göran Ekström, Bo Karlsson, Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134149451</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591213</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6559053</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson, Bo Karlsson, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134318475</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>591072</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6559189</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134318463</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99504</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>591072</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6559189</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134318435</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>591072</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6559189</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134318301</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långstjärten O om , Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>591072</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6559189</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134297169</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långstjärten ONO om , Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>591239</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6559260</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25118-2026 artfynd.xlsx
+++ b/artfynd/A 25118-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139578</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139574</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318320</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134297109</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139583</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134149270</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1698,6 +1743,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134149427</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134314782</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318567</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2019,6 +2079,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318573</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2130,6 +2195,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139582</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134149451</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2344,6 +2419,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318475</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2451,6 +2531,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318463</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2558,6 +2643,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2665,6 +2755,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134318301</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2768,8 +2863,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134297169</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>